--- a/artfynd/A 40224-2022 artfynd.xlsx
+++ b/artfynd/A 40224-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40224-2022 artfynd.xlsx
+++ b/artfynd/A 40224-2022 artfynd.xlsx
@@ -1276,7 +1276,7 @@
         <v>95412287</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1321,10 +1321,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466232.2934523974</v>
+        <v>466232</v>
       </c>
       <c r="R7" t="n">
-        <v>6718990.364524492</v>
+        <v>6718991</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1354,19 +1354,9 @@
           <t>2021-08-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-08-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 40224-2022 artfynd.xlsx
+++ b/artfynd/A 40224-2022 artfynd.xlsx
@@ -1276,7 +1276,7 @@
         <v>95412287</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 40224-2022 artfynd.xlsx
+++ b/artfynd/A 40224-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95411943</v>
+        <v>95412454</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,25 +686,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -718,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466289.1380198324</v>
+        <v>466211</v>
       </c>
       <c r="R2" t="n">
-        <v>6718967.24081999</v>
+        <v>6718968</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,19 +754,9 @@
           <t>2021-08-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-08-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95412454</v>
+        <v>95532470</v>
       </c>
       <c r="B3" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,28 +812,17 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skramsen NO, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466211.423252948</v>
+        <v>466260</v>
       </c>
       <c r="R3" t="n">
-        <v>6718967.969250771</v>
+        <v>6719015</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,22 +849,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,7 +863,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -908,60 +874,52 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95412039</v>
+        <v>95532473</v>
       </c>
       <c r="B4" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skramsen NO, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466253.9308009573</v>
+        <v>466124</v>
       </c>
       <c r="R4" t="n">
-        <v>6718989.670561598</v>
+        <v>6718975</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -988,27 +946,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På asp rikligt.</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,7 +960,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1029,22 +971,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95411807</v>
+        <v>95532474</v>
       </c>
       <c r="B5" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,19 +1007,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skramsen NO, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466292.4569580855</v>
+        <v>466108</v>
       </c>
       <c r="R5" t="n">
-        <v>6718953.949716845</v>
+        <v>6718958</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,22 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1057,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1145,63 +1068,66 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95412632</v>
+        <v>95890989</v>
       </c>
       <c r="B6" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6450</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skramsen NO, Dlr</t>
+          <t>Skramsen, NO, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466111.950201211</v>
+        <v>466227</v>
       </c>
       <c r="R6" t="n">
-        <v>6718852.01760059</v>
+        <v>6718885</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,27 +1151,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På stor klippa.</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,27 +1182,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95412287</v>
+        <v>95490370</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,31 +1205,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5741</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1321,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466232</v>
+        <v>466248</v>
       </c>
       <c r="R7" t="n">
-        <v>6718991</v>
+        <v>6719001</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1359,12 +1278,18 @@
           <t>2021-08-10</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>En rätt stor fk.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1383,37 +1308,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95412601</v>
+        <v>95411943</v>
       </c>
       <c r="B8" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1426,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466127.2471417623</v>
+        <v>466289</v>
       </c>
       <c r="R8" t="n">
-        <v>6718909.335137485</v>
+        <v>6718967</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1459,24 +1379,9 @@
           <t>2021-08-10</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-08-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Bränd stubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,53 +1409,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95412685</v>
+        <v>95532458</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skramsen NO, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466106.5672396038</v>
+        <v>466254</v>
       </c>
       <c r="R9" t="n">
-        <v>6718855.015028773</v>
+        <v>6719026</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1577,27 +1474,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt på aspstam.</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,7 +1488,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1618,60 +1499,52 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95412574</v>
+        <v>95532459</v>
       </c>
       <c r="B10" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skramsen NO, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466181.6253634302</v>
+        <v>466199</v>
       </c>
       <c r="R10" t="n">
-        <v>6718937.799949669</v>
+        <v>6719053</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1698,27 +1571,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På bränd stubbe.</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,7 +1585,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1739,72 +1596,56 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>95412328</v>
+        <v>95889866</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skramsen NO, Dlr</t>
+          <t>Skramsen, NO, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466209.060703111</v>
+        <v>466165</v>
       </c>
       <c r="R11" t="n">
-        <v>6718978.304748794</v>
+        <v>6718825</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1828,22 +1669,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,56 +1693,50 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>95411954</v>
+        <v>95412601</v>
       </c>
       <c r="B12" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1914,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466289.1472149284</v>
+        <v>466127</v>
       </c>
       <c r="R12" t="n">
-        <v>6718968.222956545</v>
+        <v>6718909</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1947,24 +1782,14 @@
           <t>2021-08-10</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-08-10</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Bränd stubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1992,56 +1817,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>95411973</v>
+        <v>95890834</v>
       </c>
       <c r="B13" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skramsen NO, Dlr</t>
+          <t>Skramsen, NO, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466271.0723918921</v>
+        <v>466221</v>
       </c>
       <c r="R13" t="n">
-        <v>6718981.65220491</v>
+        <v>6718786</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2065,27 +1883,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2094,83 +1907,67 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>95490370</v>
+        <v>95891039</v>
       </c>
       <c r="B14" t="n">
-        <v>88921</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5741</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skramsen NO, Dlr</t>
+          <t>Skramsen, NO, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466248.1297193331</v>
+        <v>466234</v>
       </c>
       <c r="R14" t="n">
-        <v>6719000.529304939</v>
+        <v>6718879</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2194,63 +1991,52 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>En rätt stor fk.</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>95530343</v>
+        <v>95412632</v>
       </c>
       <c r="B15" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2258,34 +2044,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>6450</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skramsen NO, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466431.8443636021</v>
+        <v>466112</v>
       </c>
       <c r="R15" t="n">
-        <v>6719183.954353156</v>
+        <v>6718852</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2312,27 +2101,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>6 mindre fk.</t>
+          <t>På stor klippa.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2341,6 +2120,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2352,22 +2132,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>95532467</v>
+        <v>95412574</v>
       </c>
       <c r="B16" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,34 +2150,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skramsen NO, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466381.9442682731</v>
+        <v>466182</v>
       </c>
       <c r="R16" t="n">
-        <v>6719160.356861604</v>
+        <v>6718938</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2429,22 +2207,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På bränd stubbe.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2453,6 +2226,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2464,57 +2238,55 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>95532443</v>
+        <v>95411954</v>
       </c>
       <c r="B17" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skramsen NO, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466350.3693649332</v>
+        <v>466289</v>
       </c>
       <c r="R17" t="n">
-        <v>6718623.856133976</v>
+        <v>6718968</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2541,22 +2313,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2565,6 +2332,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2576,22 +2344,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>95532442</v>
+        <v>95411973</v>
       </c>
       <c r="B18" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,34 +2362,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skramsen NO, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466445.6523817014</v>
+        <v>466271</v>
       </c>
       <c r="R18" t="n">
-        <v>6719187.75429108</v>
+        <v>6718982</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2653,22 +2419,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-10</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2677,6 +2438,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2688,22 +2450,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>95532461</v>
+        <v>95412039</v>
       </c>
       <c r="B19" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,34 +2468,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6450</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skramsen NO, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466391.4899756311</v>
+        <v>466254</v>
       </c>
       <c r="R19" t="n">
-        <v>6718707.459140752</v>
+        <v>6718989</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2765,22 +2525,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På asp rikligt.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2789,6 +2544,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2800,22 +2556,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>95530332</v>
+        <v>95890477</v>
       </c>
       <c r="B20" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,37 +2574,47 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skramsen NO, Dlr</t>
+          <t>Skramsen, NO, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466394.3680528478</v>
+        <v>466186</v>
       </c>
       <c r="R20" t="n">
-        <v>6718699.573929941</v>
+        <v>6718757</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2877,22 +2638,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2907,62 +2668,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>95530331</v>
+        <v>95412685</v>
       </c>
       <c r="B21" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skramsen NO, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466356.3319625578</v>
+        <v>466107</v>
       </c>
       <c r="R21" t="n">
-        <v>6718630.185470104</v>
+        <v>6718855</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2989,27 +2748,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>5 fk.</t>
+          <t>Rikligt på aspstam.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3018,6 +2767,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3029,22 +2779,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>95532469</v>
+        <v>95412287</v>
       </c>
       <c r="B22" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3052,34 +2797,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skramsen NO, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466444.6595579273</v>
+        <v>466232</v>
       </c>
       <c r="R22" t="n">
-        <v>6719186.781381917</v>
+        <v>6718991</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3106,22 +2859,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3141,57 +2884,64 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>95530325</v>
+        <v>95412328</v>
       </c>
       <c r="B23" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skramsen NO, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466394.3680528478</v>
+        <v>466209</v>
       </c>
       <c r="R23" t="n">
-        <v>6718699.573929941</v>
+        <v>6718978</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3218,22 +2968,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3242,6 +2982,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3253,60 +2994,70 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>95532447</v>
+        <v>95890045</v>
       </c>
       <c r="B24" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skramsen NO, Dlr</t>
+          <t>Skramsen, NO, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466364.122417165</v>
+        <v>466184</v>
       </c>
       <c r="R24" t="n">
-        <v>6718726.869327344</v>
+        <v>6718835</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3330,22 +3081,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Inom 3 m radie.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3360,65 +3116,62 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>95532453</v>
+        <v>95890871</v>
       </c>
       <c r="B25" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skramsen NO, Dlr</t>
+          <t>Skramsen, NO, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466360.872829864</v>
+        <v>466221</v>
       </c>
       <c r="R25" t="n">
-        <v>6718694.975191399</v>
+        <v>6718786</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3442,22 +3195,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3472,65 +3225,75 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>95532450</v>
+        <v>95890931</v>
       </c>
       <c r="B26" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skramsen NO, Dlr</t>
+          <t>Skramsen, NO, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466350.3693649332</v>
+        <v>466220</v>
       </c>
       <c r="R26" t="n">
-        <v>6718623.856133976</v>
+        <v>6718835</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3554,22 +3317,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3584,27 +3347,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>95890385</v>
+        <v>95889820</v>
       </c>
       <c r="B27" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3629,16 +3387,7 @@
           <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3646,10 +3395,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466189.8397094292</v>
+        <v>466135</v>
       </c>
       <c r="R27" t="n">
-        <v>6718764.845949437</v>
+        <v>6718806</v>
       </c>
       <c r="S27" t="n">
         <v>16</v>
@@ -3681,7 +3430,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3691,7 +3440,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3718,55 +3467,58 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>95890871</v>
+        <v>95890385</v>
       </c>
       <c r="B28" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skramsen, NO, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466220.5305843108</v>
+        <v>466190</v>
       </c>
       <c r="R28" t="n">
-        <v>6718785.185701799</v>
+        <v>6718765</v>
       </c>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3795,7 +3547,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3805,7 +3557,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3832,15 +3584,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>95891050</v>
+        <v>95890586</v>
       </c>
       <c r="B29" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3865,16 +3612,7 @@
           <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3882,13 +3620,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466234.1946973287</v>
+        <v>466231</v>
       </c>
       <c r="R29" t="n">
-        <v>6718878.372242305</v>
+        <v>6718747</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3917,7 +3655,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3927,7 +3665,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Brandljudsstubbe på skvattramtallmossen nedan sluttningen.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3954,37 +3697,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>95889866</v>
+        <v>95890642</v>
       </c>
       <c r="B30" t="n">
-        <v>77532</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3995,13 +3733,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466165.3114927084</v>
+        <v>466250</v>
       </c>
       <c r="R30" t="n">
-        <v>6718824.503692268</v>
+        <v>6718785</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4030,7 +3768,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4040,7 +3778,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4067,15 +3805,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>95890867</v>
+        <v>95890718</v>
       </c>
       <c r="B31" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4100,7 +3833,16 @@
           <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4108,10 +3850,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466220.5305843108</v>
+        <v>466237</v>
       </c>
       <c r="R31" t="n">
-        <v>6718785.185701799</v>
+        <v>6718784</v>
       </c>
       <c r="S31" t="n">
         <v>12</v>
@@ -4143,7 +3885,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4153,7 +3895,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4180,49 +3922,35 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>95890477</v>
+        <v>95890867</v>
       </c>
       <c r="B32" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4230,10 +3958,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466185.8307779917</v>
+        <v>466221</v>
       </c>
       <c r="R32" t="n">
-        <v>6718757.025356704</v>
+        <v>6718786</v>
       </c>
       <c r="S32" t="n">
         <v>12</v>
@@ -4265,7 +3993,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4275,7 +4003,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4305,12 +4033,7 @@
         <v>95891023</v>
       </c>
       <c r="B33" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4352,10 +4075,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466231.3447493512</v>
+        <v>466231</v>
       </c>
       <c r="R33" t="n">
-        <v>6718889.203672025</v>
+        <v>6718889</v>
       </c>
       <c r="S33" t="n">
         <v>8</v>
@@ -4429,15 +4152,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>95891039</v>
+        <v>95891050</v>
       </c>
       <c r="B34" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4445,24 +4163,33 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4470,10 +4197,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466234.1946973287</v>
+        <v>466234</v>
       </c>
       <c r="R34" t="n">
-        <v>6718878.372242305</v>
+        <v>6718879</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4542,15 +4269,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>95890834</v>
+        <v>95891081</v>
       </c>
       <c r="B35" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4558,24 +4280,33 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4583,13 +4314,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466220.5305843108</v>
+        <v>466244</v>
       </c>
       <c r="R35" t="n">
-        <v>6718785.185701799</v>
+        <v>6718899</v>
       </c>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4618,7 +4349,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4628,7 +4359,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4655,68 +4386,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>95890045</v>
+        <v>95532466</v>
       </c>
       <c r="B36" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skramsen, NO, Dlr</t>
+          <t>Skramsen NO, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466184.0999787676</v>
+        <v>466444</v>
       </c>
       <c r="R36" t="n">
-        <v>6718834.640939083</v>
+        <v>6719187</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4740,27 +4451,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>18:54</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>18:54</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Inom 3 m radie.</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4775,27 +4471,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>95890586</v>
+        <v>95532467</v>
       </c>
       <c r="B37" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4803,38 +4494,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skramsen, NO, Dlr</t>
+          <t>Skramsen NO, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466230.00456033</v>
+        <v>466382</v>
       </c>
       <c r="R37" t="n">
-        <v>6718746.296863541</v>
+        <v>6719160</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4858,27 +4548,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Brandljudsstubbe på skvattramtallmossen nedan sluttningen.</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4893,80 +4568,63 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>95890931</v>
+        <v>95411807</v>
       </c>
       <c r="B38" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skramsen, NO, Dlr</t>
+          <t>Skramsen NO, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466220.0167114146</v>
+        <v>466293</v>
       </c>
       <c r="R38" t="n">
-        <v>6718835.286081408</v>
+        <v>6718954</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4990,22 +4648,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>19:50</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>19:50</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5014,33 +4662,29 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>95891081</v>
+        <v>95530331</v>
       </c>
       <c r="B39" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5048,47 +4692,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skramsen, NO, Dlr</t>
+          <t>Skramsen NO, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466244.2302107442</v>
+        <v>466357</v>
       </c>
       <c r="R39" t="n">
-        <v>6718899.396403954</v>
+        <v>6718630</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5112,22 +4746,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>20:09</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>20:09</t>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>5 fk.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5142,31 +4771,26 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>95890989</v>
+        <v>95530332</v>
       </c>
       <c r="B40" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -5187,31 +4811,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skramsen, NO, Dlr</t>
+          <t>Skramsen NO, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466227.3728912233</v>
+        <v>466395</v>
       </c>
       <c r="R40" t="n">
-        <v>6718885.311943273</v>
+        <v>6718699</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5235,22 +4848,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>19:55</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>19:55</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5259,22 +4862,802 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>95530325</v>
+      </c>
+      <c r="B41" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Skramsen NO, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>466395</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6718699</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>95530343</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Skramsen NO, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>466432</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6719184</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>6 mindre fk.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>95532443</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skramsen NO, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>466351</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6718624</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>95532461</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Skramsen NO, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>466392</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6718707</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>95532453</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Skramsen NO, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>466361</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6718695</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>95532442</v>
+      </c>
+      <c r="B46" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Skramsen NO, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>466445</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6719188</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>95532447</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Skramsen NO, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>466364</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6718727</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>95532450</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Skramsen NO, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>466351</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6718624</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Jonas Pehrs</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40224-2022 artfynd.xlsx
+++ b/artfynd/A 40224-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95412454</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95532466</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95532467</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95532470</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95411807</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,6 +1300,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95532473</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,6 +1402,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95532474</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1469,6 +1509,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95530331</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1566,6 +1611,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95530332</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1685,6 +1735,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95890989</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1782,6 +1837,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95530325</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95530343</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95490370</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2099,6 +2169,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95411943</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2196,6 +2271,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95532458</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2293,6 +2373,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95532459</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2401,6 +2486,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95889866</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2507,6 +2597,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95412601</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2604,6 +2699,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95532443</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2712,6 +2812,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95890834</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2820,6 +2925,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95891039</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2926,6 +3036,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95412632</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3023,6 +3138,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95532461</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3129,6 +3249,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95412574</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3226,6 +3351,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95532453</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3332,6 +3462,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95411954</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3438,6 +3573,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95411973</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3544,6 +3684,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95412039</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3661,6 +3806,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95890477</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3767,6 +3917,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95412685</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3872,6 +4027,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95412287</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3969,6 +4129,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95532442</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4079,6 +4244,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95412328</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4206,6 +4376,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95890045</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4315,6 +4490,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95890871</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4437,6 +4617,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95890931</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4534,6 +4719,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95532447</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4631,6 +4821,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95532450</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4739,6 +4934,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95889820</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4856,6 +5056,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95890385</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4969,6 +5174,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95890586</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5077,6 +5287,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95890642</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5194,6 +5409,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95890718</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5302,6 +5522,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95890867</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5424,6 +5649,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95891023</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5541,6 +5771,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95891050</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5658,8 +5893,62 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95891081</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>